--- a/TrafagSalesExporter/docs/Issue_Log_Konsolidiert_2026-08-12.xlsx
+++ b/TrafagSalesExporter/docs/Issue_Log_Konsolidiert_2026-08-12.xlsx
@@ -402,16 +402,19 @@
     <x:t>247 Zeilen haben gar kein Datum</x:t>
   </x:si>
   <x:si>
-    <x:t>FacturasTB im Exportskript joinen und FechaAsiento als PostingDate ausgeben, danach im ES-Mapping auf SalesRecord.PostingDate mappen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>docs/FINANCE_ISSUE_LOG_ANDREAS_2026-07-28.md §1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Join-Schlüssel zu den Lieferscheinpositionen offen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PostingDate fehlt bei 5'712 von 5'712 ES-Zeilen (100 %), am 12.08.2026 erneut gemessen. Die Fallback-Kette PostingDate zu InvoiceDate rettet die meisten Zeilen, aber 247 Zeilen haben gar kein Datum und fallen aus jeder Jahres- und Monatsauswertung. Am 28.07. waren es 229, die Zahl wächst also. Sage hat das Buchungsdatum als FacturasTB.FechaAsiento, in der Stichprobe zu 100 % gefüllt. Offen sind der Join-Schlüssel und die Behandlung von Gutschriften. Nebenbefund: UK hat 16 Zeilen ohne jedes Datum, vorher 6. WICHTIGE KORREKTUR am 12.08.2026 gegenüber der Analyse vom 28.07.: diese Zeilen fallen NICHT aus der Auswertung heraus, sie sind schlimmer eingeordnet. Die Spalte Finance | Date im Gesamtexport nutzt die Fallback-Kette bis zum ExtractionDate, deshalb landen sie im Monat des Exportlaufs. Nachgerechnet: Spanien hat im August 2026 nach Belegdatum 86 Zeilen, im Export aber 336, Differenz genau 250; UK 91 gegenüber 107, Differenz genau 16. Der laufende Monat wird also um 266 Zeilen aufgeblasen, die fachlich in andere Perioden gehören.</x:t>
+    <x:t>Paket auf den spanischen Sage-Server kopieren, Export einmal laufen lassen und dabei die Zeilenzahl gegen den Vorlauf prüfen, danach PostingDate beim Standort Spanien zuordnen und reimportieren</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SageSpainExportPackage/SageSpainFinalExportPackage/Export-SageSpainSalesCsv.ps1; Run-SpainRangeExportAndUpload-AllInOne.ps1; docs/FINANCE_ES_BUCHUNGSDATUM_2026-08-03.md Abschnitt 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RDP-Sitzung auf dem spanischen Sage-Server; Join-Schlüssel bis zur Messung eine Annahme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAND 17.08.2026: das Feld ist im Exportskript EINGEBAUT und wartet nur noch auf den Lauf in Spanien. Die SQL selektiert FacturasTB.FechaAsiento als PostingDate und FacturasTB.Asiento als PostingDocument, per OUTER APPLY mit TOP 1 statt JOIN, weil 70 von 3'642 Rechnungsschlüsseln mehrere Buchungszeilen haben und ein JOIN die Verkaufszeilen vervielfacht hätte. Belegt ist bisher NUR die Syntax (ScriptDom, alle vier Varianten, mit Gegenprobe); Trefferquote, Schlüsselrichtigkeit und Gutschriften sind offen. Beim ersten Lauf zwingend die Zeilenzahl gegen den Vorlauf prüfen. Nebenbefund: die Paket-Zip war seit dem rclone-Fix veraltet und wurde neu gebaut. PostingDate fehlt bei 5'712 von 5'712 ES-Zeilen (100 %), am 12.08.2026 erneut gemessen. Die Fallback-Kette PostingDate zu InvoiceDate rettet die meisten Zeilen, aber 247 Zeilen haben gar kein Datum und fallen aus jeder Jahres- und Monatsauswertung. Am 28.07. waren es 229, die Zahl wächst also. Sage hat das Buchungsdatum als FacturasTB.FechaAsiento, in der Stichprobe zu 100 % gefüllt. Offen sind der Join-Schlüssel und die Behandlung von Gutschriften. Nebenbefund: UK hat 16 Zeilen ohne jedes Datum, vorher 6. WICHTIGE KORREKTUR am 12.08.2026 gegenüber der Analyse vom 28.07.: diese Zeilen fallen NICHT aus der Auswertung heraus, sie sind schlimmer eingeordnet. Die Spalte Finance | Date im Gesamtexport nutzt die Fallback-Kette bis zum ExtractionDate, deshalb landen sie im Monat des Exportlaufs. Nachgerechnet: Spanien hat im August 2026 nach Belegdatum 86 Zeilen, im Export aber 336, Differenz genau 250; UK 91 gegenüber 107, Differenz genau 16. Der laufende Monat wird also um 266 Zeilen aufgeblasen, die fachlich in andere Perioden gehören.</x:t>
   </x:si>
   <x:si>
     <x:t>ISS-004.3</x:t>
@@ -1983,8 +1986,8 @@
       <x:c r="E14" s="9" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="F14" s="12" t="s">
-        <x:v>74</x:v>
+      <x:c r="F14" s="5" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G14" s="7" t="s">
         <x:v>75</x:v>
@@ -2005,13 +2008,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="M14" s="7" t="s">
-        <x:v>26</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="N14" s="9" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="O14" s="9" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:15">
@@ -2019,13 +2022,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="8" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C15" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D15" s="9" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E15" s="9" t="s">
         <x:v>25</x:v>
@@ -2040,10 +2043,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="I15" s="9" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J15" s="9" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K15" s="7" t="s">
         <x:v>61</x:v>
@@ -2058,7 +2061,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O15" s="9" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:15">
@@ -2066,16 +2069,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F16" s="10" t="s">
         <x:v>32</x:v>
@@ -2087,10 +2090,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="I16" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="J16" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="K16" s="2" t="s">
         <x:v>61</x:v>
@@ -2105,7 +2108,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O16" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:15">
@@ -2113,13 +2116,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E17" s="4" t="s">
         <x:v>25</x:v>
@@ -2131,16 +2134,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="I17" s="4" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="J17" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K17" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="L17" s="2" t="s">
         <x:v>25</x:v>
@@ -2149,10 +2152,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="N17" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="O17" s="4" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:15">
@@ -2160,16 +2163,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E18" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F18" s="5" t="s">
         <x:v>19</x:v>
@@ -2181,10 +2184,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="I18" s="4" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J18" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="K18" s="2" t="s">
         <x:v>52</x:v>
@@ -2199,7 +2202,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O18" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:15">
@@ -2207,13 +2210,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D19" s="9" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E19" s="9" t="s">
         <x:v>25</x:v>
@@ -2225,19 +2228,19 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="H19" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="I19" s="9" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="J19" s="9" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K19" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L19" s="7" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="M19" s="7" t="s">
         <x:v>26</x:v>
@@ -2246,7 +2249,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O19" s="9" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:15">
@@ -2254,13 +2257,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E20" s="4" t="s">
         <x:v>25</x:v>
@@ -2272,16 +2275,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H20" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="I20" s="4" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="J20" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="K20" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="L20" s="2" t="s">
         <x:v>25</x:v>
@@ -2290,10 +2293,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="N20" s="4" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="O20" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:15">
@@ -2301,13 +2304,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E21" s="4" t="s">
         <x:v>25</x:v>
@@ -2319,16 +2322,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="H21" s="2" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="I21" s="4" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="J21" s="4" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="K21" s="2" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="L21" s="2" t="s">
         <x:v>25</x:v>
@@ -2337,10 +2340,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="N21" s="4" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="O21" s="4" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:15">
@@ -2348,13 +2351,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E22" s="4" t="s">
         <x:v>25</x:v>
@@ -2369,25 +2372,25 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="I22" s="4" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J22" s="4" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K22" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="L22" s="2" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="M22" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="N22" s="4" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="O22" s="4" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:15">
@@ -2395,13 +2398,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C23" s="4" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E23" s="4" t="s">
         <x:v>25</x:v>
@@ -2416,10 +2419,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="I23" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J23" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K23" s="2" t="s">
         <x:v>52</x:v>
@@ -2434,7 +2437,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O23" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:15">
@@ -2442,16 +2445,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C24" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E24" s="4" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>74</x:v>
@@ -2463,13 +2466,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="I24" s="4" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="J24" s="4" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K24" s="2" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="L24" s="2" t="s">
         <x:v>25</x:v>
@@ -2481,7 +2484,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O24" s="4" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:15">
@@ -2489,16 +2492,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E25" s="4" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F25" s="12" t="s">
         <x:v>74</x:v>
@@ -2510,10 +2513,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="I25" s="4" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="J25" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K25" s="2" t="s">
         <x:v>26</x:v>
@@ -2528,7 +2531,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O25" s="4" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:15">
@@ -2536,16 +2539,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C26" s="4" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E26" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F26" s="13" t="s">
         <x:v>103</x:v>
@@ -2554,13 +2557,13 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="H26" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="I26" s="4" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="J26" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K26" s="2" t="s">
         <x:v>26</x:v>
@@ -2575,7 +2578,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="O26" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:15">
@@ -2583,16 +2586,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="8" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D27" s="9" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E27" s="9" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
         <x:v>74</x:v>
@@ -2604,10 +2607,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="I27" s="9" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="J27" s="9" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K27" s="7" t="s">
         <x:v>26</x:v>
@@ -2622,7 +2625,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="O27" s="9" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2649,82 +2652,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="15" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B1" s="16" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2" ht="46" customHeight="1">
       <x:c r="A2" s="17" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B2" s="14" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" ht="46" customHeight="1">
       <x:c r="A3" s="17" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B3" s="14" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2" ht="46" customHeight="1">
       <x:c r="A4" s="17" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2" ht="46" customHeight="1">
       <x:c r="A5" s="17" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B5" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2" ht="46" customHeight="1">
       <x:c r="A6" s="17" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B6" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2" ht="46" customHeight="1">
       <x:c r="A7" s="17" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B7" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2" ht="46" customHeight="1">
       <x:c r="A8" s="17" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B8" s="14" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="46" customHeight="1">
       <x:c r="A9" s="17" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B9" s="14" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2" ht="46" customHeight="1">
       <x:c r="A10" s="17" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B10" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
